--- a/tame_output/ON/bt/strategyON_20240725.xlsx
+++ b/tame_output/ON/bt/strategyON_20240725.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-553.7%</t>
+          <t>-553.0%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.3%</t>
+          <t>-152.1%</t>
         </is>
       </c>
     </row>
@@ -48356,10 +48356,10 @@
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-3.921324180663445</v>
+        <v>-3.914461474262619</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.238729607581305</v>
+        <v>2.241474690141635</v>
       </c>
       <c r="F2035" t="n">
         <v>0.7128186895082853</v>

--- a/tame_output/ON/bt/strategyON_20240725.xlsx
+++ b/tame_output/ON/bt/strategyON_20240725.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.3%</t>
+          <t>455.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-553.0%</t>
+          <t>-565.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-127.7%</t>
+          <t>-120.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-166.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-31.0%</t>
         </is>
       </c>
     </row>
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.593788845959513</v>
+        <v>-2.735115163585778</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.490851456573458</v>
+        <v>2.434320929522952</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8115847362381446</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.100470051589657</v>
+        <v>4.015674261013897</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.670118823560419</v>
+        <v>-2.811445141186684</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.458431278426871</v>
+        <v>2.401900751376365</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8115847362381446</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.098581864483432</v>
+        <v>4.013786073907673</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.78187577617572</v>
+        <v>-2.923202093801985</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.408548726983613</v>
+        <v>2.352018199933107</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8411541012491086</v>
+        <v>0.6998277836228435</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.026347922517113</v>
+        <v>3.941552131941354</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.780034757117468</v>
+        <v>-2.921361074743734</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.407719144817065</v>
+        <v>2.351188617766559</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7010960102943119</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.025542868730146</v>
+        <v>3.940747078154387</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.912336049215022</v>
+        <v>-3.053662366841287</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.367872034843963</v>
+        <v>2.311341507793457</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7010960102943119</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.038616275596065</v>
+        <v>3.953820485020306</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.913897692029882</v>
+        <v>-3.055224009656147</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.367247377718019</v>
+        <v>2.310716850667513</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7010960102943119</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.038616275596065</v>
+        <v>3.953820485020306</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.941798479139355</v>
+        <v>-3.08312479676562</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.354611104001231</v>
+        <v>2.298080576950725</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8078254037776422</v>
+        <v>0.6664990861513771</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.016382162237306</v>
+        <v>3.931586371661547</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.064324581842249</v>
+        <v>-3.205650899468514</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.302365106897272</v>
+        <v>2.245834579846766</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6852993010747483</v>
+        <v>0.5439729834484832</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.939630944592769</v>
+        <v>3.854835154017009</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.084385903118755</v>
+        <v>-3.225712220745021</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.361046537977174</v>
+        <v>2.304516010926668</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6652379797982413</v>
+        <v>0.5239116621719762</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.994300111417368</v>
+        <v>3.909504320841609</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.341106721113579</v>
+        <v>-3.482433038739845</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.398669929781091</v>
+        <v>2.342139402730585</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.069563085932926</v>
+        <v>3.984767295357167</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.49509313888972</v>
+        <v>-3.636419456515985</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.406055631816275</v>
+        <v>2.349525104765768</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.138543355078566</v>
+        <v>4.053747564502807</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.444571235062054</v>
+        <v>-3.585897552688319</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.412315595467462</v>
+        <v>2.355785068416956</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.124594557198687</v>
+        <v>4.039798766622928</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.697046389069778</v>
+        <v>-3.838372706696044</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.323196022919786</v>
+        <v>2.26666549586928</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.136465046254101</v>
+        <v>4.051669255678342</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.966519190991487</v>
+        <v>-4.107845508617752</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.216617436670047</v>
+        <v>2.16008690961954</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.137675580773045</v>
+        <v>4.052879790197285</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.124063262720928</v>
+        <v>-4.265389580347193</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.157721550205591</v>
+        <v>2.101191023155085</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.489921600514152</v>
+        <v>0.3485952828878868</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.101656239916202</v>
+        <v>4.016860449340443</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.402027658304202</v>
+        <v>-4.543353975930467</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.041613644708471</v>
+        <v>1.985083117657966</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2589755486024026</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.0429622520811</v>
+        <v>3.958166461505341</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.518995350943093</v>
+        <v>-4.660321668569358</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.157030624351959</v>
+        <v>2.100500097301453</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2589755486024026</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.205166308780145</v>
+        <v>4.120370518204385</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.603713293164046</v>
+        <v>-4.745039610790311</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.117990085427392</v>
+        <v>2.061459558376886</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3151858373006214</v>
+        <v>0.1738595196743562</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.148943329387131</v>
+        <v>4.064147538811372</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.685648111432929</v>
+        <v>-4.826974429059194</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.095445575688331</v>
+        <v>2.038915048637824</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3052510917135412</v>
+        <v>0.163924774087276</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.153211899603374</v>
+        <v>4.068416109027615</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.631909938032667</v>
+        <v>-4.773236255658932</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.125866483504337</v>
+        <v>2.069335956453831</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3589892651138033</v>
+        <v>0.2176629474875381</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.194380442099433</v>
+        <v>4.109584651523674</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.521903654555445</v>
+        <v>-4.663229972181711</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.162021884139402</v>
+        <v>2.105491357088896</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3821938370310785</v>
+        <v>0.2408675194048133</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.200456072493974</v>
+        <v>4.115660281918215</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.37884407881452</v>
+        <v>-4.520170396440784</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.223495725157746</v>
+        <v>2.16696519810724</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3902072636210578</v>
+        <v>0.2488809459947926</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.209514139169936</v>
+        <v>4.124718348594177</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.077397353342683</v>
+        <v>-4.218723670968947</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.351335298229017</v>
+        <v>2.294804771178512</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5503276714666299</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.397643057335575</v>
+        <v>4.312847266759816</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.132352549785752</v>
+        <v>-4.273678867412016</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.3303243974045</v>
+        <v>2.273793870353994</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5503276714666299</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.398614235088285</v>
+        <v>4.313818444512526</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.081314173779232</v>
+        <v>-4.222640491405496</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.351582652186863</v>
+        <v>2.295052125136358</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5503276714666299</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.399457139468041</v>
+        <v>4.314661348892281</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.040174878912601</v>
+        <v>-4.181501196538865</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.387076469007662</v>
+        <v>2.330545941957156</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7327932839595258</v>
+        <v>0.5914669663332607</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.443178815262165</v>
+        <v>4.358383024686406</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.929568738832999</v>
+        <v>-4.070895056459263</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.247502921163437</v>
+        <v>2.190972394112931</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8433994240391278</v>
+        <v>0.7020731064128627</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.325726495433861</v>
+        <v>4.240930704858101</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.060149473363841</v>
+        <v>-4.201475790990106</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.198772671425063</v>
+        <v>2.142242144374558</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7128186895082853</v>
+        <v>0.5714923718820202</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.250880098789318</v>
+        <v>4.166084308213559</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.740410528471517</v>
+        <v>3.725148474878258</v>
       </c>
       <c r="C2035" t="n">
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-3.914461474262619</v>
+        <v>-4.036979456799144</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.241474690141635</v>
+        <v>2.192467497127025</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7128186895082853</v>
+        <v>0.5714923718820202</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.235306917865401</v>
+        <v>4.150511127289642</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240725.xlsx
+++ b/tame_output/ON/bt/strategyON_20240725.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.9%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.6%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.2%</t>
+          <t>455.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-565.3%</t>
+          <t>-565.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-157.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-120.8%</t>
+          <t>-127.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.8%</t>
+          <t>-152.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-72.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2035"/>
+  <dimension ref="A1:G2036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.735115163585778</v>
+        <v>-2.593788845959513</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.434320929522952</v>
+        <v>2.490851456573458</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8115847362381446</v>
+        <v>0.9529110538644098</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.015674261013897</v>
+        <v>4.100470051589657</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.811445141186684</v>
+        <v>-2.670118823560419</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.401900751376365</v>
+        <v>2.458431278426871</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8115847362381446</v>
+        <v>0.9529110538644098</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.013786073907673</v>
+        <v>4.098581864483432</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.923202093801985</v>
+        <v>-2.78187577617572</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.352018199933107</v>
+        <v>2.408548726983613</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6998277836228435</v>
+        <v>0.8411541012491086</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.941552131941354</v>
+        <v>4.026347922517113</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.921361074743734</v>
+        <v>-2.780034757117468</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.351188617766559</v>
+        <v>2.407719144817065</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7010960102943119</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.940747078154387</v>
+        <v>4.025542868730146</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.053662366841287</v>
+        <v>-2.912336049215022</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.311341507793457</v>
+        <v>2.367872034843963</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7010960102943119</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.953820485020306</v>
+        <v>4.038616275596065</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.055224009656147</v>
+        <v>-2.913897692029882</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.310716850667513</v>
+        <v>2.367247377718019</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7010960102943119</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.953820485020306</v>
+        <v>4.038616275596065</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.08312479676562</v>
+        <v>-2.941798479139355</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.298080576950725</v>
+        <v>2.354611104001231</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6664990861513771</v>
+        <v>0.8078254037776422</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.931586371661547</v>
+        <v>4.016382162237306</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.205650899468514</v>
+        <v>-3.064324581842249</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.245834579846766</v>
+        <v>2.302365106897272</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5439729834484832</v>
+        <v>0.6852993010747483</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.854835154017009</v>
+        <v>3.939630944592769</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.225712220745021</v>
+        <v>-3.084385903118755</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.304516010926668</v>
+        <v>2.361046537977174</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5239116621719762</v>
+        <v>0.6652379797982413</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.909504320841609</v>
+        <v>3.994300111417368</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.482433038739845</v>
+        <v>-3.341106721113579</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.342139402730585</v>
+        <v>2.398669929781091</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.984767295357167</v>
+        <v>4.069563085932926</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.636419456515985</v>
+        <v>-3.49509313888972</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.349525104765768</v>
+        <v>2.406055631816275</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.053747564502807</v>
+        <v>4.138543355078566</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.585897552688319</v>
+        <v>-3.444571235062054</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.355785068416956</v>
+        <v>2.412315595467462</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.039798766622928</v>
+        <v>4.124594557198687</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.838372706696044</v>
+        <v>-3.697046389069778</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.26666549586928</v>
+        <v>2.323196022919786</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.051669255678342</v>
+        <v>4.136465046254101</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.107845508617752</v>
+        <v>-3.966519190991487</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.16008690961954</v>
+        <v>2.216617436670047</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.052879790197285</v>
+        <v>4.137675580773045</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.265389580347193</v>
+        <v>-4.124063262720928</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.101191023155085</v>
+        <v>2.157721550205591</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3485952828878868</v>
+        <v>0.489921600514152</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.016860449340443</v>
+        <v>4.101656239916202</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.543353975930467</v>
+        <v>-4.402027658304202</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.985083117657966</v>
+        <v>2.041613644708471</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2589755486024026</v>
+        <v>0.4003018662286678</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.958166461505341</v>
+        <v>4.0429622520811</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.660321668569358</v>
+        <v>-4.518995350943093</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.100500097301453</v>
+        <v>2.157030624351959</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2589755486024026</v>
+        <v>0.4003018662286678</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.120370518204385</v>
+        <v>4.205166308780145</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.745039610790311</v>
+        <v>-4.603713293164046</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.061459558376886</v>
+        <v>2.117990085427392</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1738595196743562</v>
+        <v>0.3151858373006214</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.064147538811372</v>
+        <v>4.148943329387131</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.826974429059194</v>
+        <v>-4.685648111432929</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.038915048637824</v>
+        <v>2.095445575688331</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.163924774087276</v>
+        <v>0.3052510917135412</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.068416109027615</v>
+        <v>4.153211899603374</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.773236255658932</v>
+        <v>-4.631909938032667</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.069335956453831</v>
+        <v>2.125866483504337</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2176629474875381</v>
+        <v>0.3589892651138033</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.109584651523674</v>
+        <v>4.194380442099433</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.663229972181711</v>
+        <v>-4.521903654555445</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.105491357088896</v>
+        <v>2.162021884139402</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2408675194048133</v>
+        <v>0.3821938370310785</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.115660281918215</v>
+        <v>4.200456072493974</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.520170396440784</v>
+        <v>-4.37884407881452</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.16696519810724</v>
+        <v>2.223495725157746</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2488809459947926</v>
+        <v>0.3902072636210578</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.124718348594177</v>
+        <v>4.209514139169936</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.218723670968947</v>
+        <v>-4.077397353342683</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.294804771178512</v>
+        <v>2.351335298229017</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5503276714666299</v>
+        <v>0.691653989092895</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.312847266759816</v>
+        <v>4.397643057335575</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.273678867412016</v>
+        <v>-4.132352549785752</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.273793870353994</v>
+        <v>2.3303243974045</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5503276714666299</v>
+        <v>0.691653989092895</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.313818444512526</v>
+        <v>4.398614235088285</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.222640491405496</v>
+        <v>-4.081314173779232</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.295052125136358</v>
+        <v>2.351582652186863</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5503276714666299</v>
+        <v>0.691653989092895</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.314661348892281</v>
+        <v>4.399457139468041</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.181501196538865</v>
+        <v>-4.040174878912601</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.330545941957156</v>
+        <v>2.387076469007662</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5914669663332607</v>
+        <v>0.7327932839595258</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.358383024686406</v>
+        <v>4.443178815262165</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.070895056459263</v>
+        <v>-3.929568738832999</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.190972394112931</v>
+        <v>2.247502921163437</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7020731064128627</v>
+        <v>0.8433994240391278</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.240930704858101</v>
+        <v>4.325726495433861</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.201475790990106</v>
+        <v>-4.060149473363841</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.142242144374558</v>
+        <v>2.198772671425063</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5714923718820202</v>
+        <v>0.7128186895082853</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.166084308213559</v>
+        <v>4.250880098789318</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,45 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.725148474878258</v>
+        <v>3.775043021218598</v>
       </c>
       <c r="C2035" t="n">
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.036979456799144</v>
+        <v>-4.042143948533621</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.192467497127025</v>
+        <v>2.190401700433234</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5714923718820202</v>
+        <v>0.7128186895082853</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.150511127289642</v>
+        <v>4.235306917865401</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="2" t="n">
+        <v>45498</v>
+      </c>
+      <c r="B2036" t="n">
+        <v>3.739351927040366</v>
+      </c>
+      <c r="C2036" t="n">
+        <v>3.743479311409944</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>-4.042143948533621</v>
+      </c>
+      <c r="E2036" t="n">
+        <v>2.190401700433234</v>
+      </c>
+      <c r="F2036" t="n">
+        <v>0.7128186895082853</v>
+      </c>
+      <c r="G2036" t="n">
+        <v>3.736543108396312</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240725.xlsx
+++ b/tame_output/ON/bt/strategyON_20240725.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-48.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.0%</t>
+          <t>455.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-565.8%</t>
+          <t>-565.3%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.2%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-127.7%</t>
+          <t>-120.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-166.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-72.0%</t>
         </is>
       </c>
     </row>
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.593788845959513</v>
+        <v>-2.735115163585778</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.490851456573458</v>
+        <v>2.434320929522952</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8115847362381446</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.100470051589657</v>
+        <v>4.015674261013897</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.670118823560419</v>
+        <v>-2.811445141186684</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.458431278426871</v>
+        <v>2.401900751376365</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.8115847362381446</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.098581864483432</v>
+        <v>4.013786073907673</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.78187577617572</v>
+        <v>-2.923202093801985</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.408548726983613</v>
+        <v>2.352018199933107</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8411541012491086</v>
+        <v>0.6998277836228435</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.026347922517113</v>
+        <v>3.941552131941354</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.780034757117468</v>
+        <v>-2.921361074743734</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.407719144817065</v>
+        <v>2.351188617766559</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7010960102943119</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.025542868730146</v>
+        <v>3.940747078154387</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.912336049215022</v>
+        <v>-3.053662366841287</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.367872034843963</v>
+        <v>2.311341507793457</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7010960102943119</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.038616275596065</v>
+        <v>3.953820485020306</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.913897692029882</v>
+        <v>-3.055224009656147</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.367247377718019</v>
+        <v>2.310716850667513</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7010960102943119</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.038616275596065</v>
+        <v>3.953820485020306</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.941798479139355</v>
+        <v>-3.08312479676562</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.354611104001231</v>
+        <v>2.298080576950725</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8078254037776422</v>
+        <v>0.6664990861513771</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.016382162237306</v>
+        <v>3.931586371661547</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.064324581842249</v>
+        <v>-3.205650899468514</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.302365106897272</v>
+        <v>2.245834579846766</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6852993010747483</v>
+        <v>0.5439729834484832</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.939630944592769</v>
+        <v>3.854835154017009</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.084385903118755</v>
+        <v>-3.225712220745021</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.361046537977174</v>
+        <v>2.304516010926668</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6652379797982413</v>
+        <v>0.5239116621719762</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.994300111417368</v>
+        <v>3.909504320841609</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.341106721113579</v>
+        <v>-3.482433038739845</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.398669929781091</v>
+        <v>2.342139402730585</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.069563085932926</v>
+        <v>3.984767295357167</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.49509313888972</v>
+        <v>-3.636419456515985</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.406055631816275</v>
+        <v>2.349525104765768</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.138543355078566</v>
+        <v>4.053747564502807</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.444571235062054</v>
+        <v>-3.585897552688319</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.412315595467462</v>
+        <v>2.355785068416956</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.124594557198687</v>
+        <v>4.039798766622928</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.697046389069778</v>
+        <v>-3.838372706696044</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.323196022919786</v>
+        <v>2.26666549586928</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.136465046254101</v>
+        <v>4.051669255678342</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.966519190991487</v>
+        <v>-4.107845508617752</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.216617436670047</v>
+        <v>2.16008690961954</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4154970880281613</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.137675580773045</v>
+        <v>4.052879790197285</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.124063262720928</v>
+        <v>-4.265389580347193</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.157721550205591</v>
+        <v>2.101191023155085</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.489921600514152</v>
+        <v>0.3485952828878868</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.101656239916202</v>
+        <v>4.016860449340443</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.402027658304202</v>
+        <v>-4.543353975930467</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.041613644708471</v>
+        <v>1.985083117657966</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2589755486024026</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.0429622520811</v>
+        <v>3.958166461505341</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.518995350943093</v>
+        <v>-4.660321668569358</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.157030624351959</v>
+        <v>2.100500097301453</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.2589755486024026</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.205166308780145</v>
+        <v>4.120370518204385</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.603713293164046</v>
+        <v>-4.745039610790311</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.117990085427392</v>
+        <v>2.061459558376886</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3151858373006214</v>
+        <v>0.1738595196743562</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.148943329387131</v>
+        <v>4.064147538811372</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.685648111432929</v>
+        <v>-4.826974429059194</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.095445575688331</v>
+        <v>2.038915048637824</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3052510917135412</v>
+        <v>0.163924774087276</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.153211899603374</v>
+        <v>4.068416109027615</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.631909938032667</v>
+        <v>-4.773236255658932</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.125866483504337</v>
+        <v>2.069335956453831</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3589892651138033</v>
+        <v>0.2176629474875381</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.194380442099433</v>
+        <v>4.109584651523674</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.521903654555445</v>
+        <v>-4.663229972181711</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.162021884139402</v>
+        <v>2.105491357088896</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3821938370310785</v>
+        <v>0.2408675194048133</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.200456072493974</v>
+        <v>4.115660281918215</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.37884407881452</v>
+        <v>-4.520170396440784</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.223495725157746</v>
+        <v>2.16696519810724</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3902072636210578</v>
+        <v>0.2488809459947926</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.209514139169936</v>
+        <v>4.124718348594177</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.077397353342683</v>
+        <v>-4.218723670968947</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.351335298229017</v>
+        <v>2.294804771178512</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5503276714666299</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.397643057335575</v>
+        <v>4.312847266759816</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.132352549785752</v>
+        <v>-4.273678867412016</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.3303243974045</v>
+        <v>2.273793870353994</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5503276714666299</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.398614235088285</v>
+        <v>4.313818444512526</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.081314173779232</v>
+        <v>-4.222640491405496</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.351582652186863</v>
+        <v>2.295052125136358</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.691653989092895</v>
+        <v>0.5503276714666299</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.399457139468041</v>
+        <v>4.314661348892281</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.040174878912601</v>
+        <v>-4.181501196538865</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.387076469007662</v>
+        <v>2.330545941957156</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7327932839595258</v>
+        <v>0.5914669663332607</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.443178815262165</v>
+        <v>4.358383024686406</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-3.929568738832999</v>
+        <v>-4.070895056459263</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.247502921163437</v>
+        <v>2.190972394112931</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8433994240391278</v>
+        <v>0.7020731064128627</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.325726495433861</v>
+        <v>4.240930704858101</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.060149473363841</v>
+        <v>-4.201475790990106</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.198772671425063</v>
+        <v>2.142242144374558</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7128186895082853</v>
+        <v>0.5714923718820202</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.250880098789318</v>
+        <v>4.166084308213559</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.042143948533621</v>
+        <v>-4.036979456799144</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.190401700433234</v>
+        <v>2.192467497127025</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7128186895082853</v>
+        <v>0.5714923718820202</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.235306917865401</v>
+        <v>4.150511127289642</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.739351927040366</v>
+        <v>3.72362336265061</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.743479311409944</v>
+        <v>3.746735483965528</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.042143948533621</v>
+        <v>-4.036979456799144</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.190401700433234</v>
+        <v>2.192467497127025</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7128186895082853</v>
+        <v>0.5714923718820202</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.736543108396312</v>
+        <v>3.739799280951896</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240725.xlsx
+++ b/tame_output/ON/bt/strategyON_20240725.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.1%</t>
+          <t>110.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.8%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.6%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.2%</t>
+          <t>455.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-565.3%</t>
+          <t>-566.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-157.6%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-120.8%</t>
+          <t>-131.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.8%</t>
+          <t>-168.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-71.9%</t>
         </is>
       </c>
     </row>
@@ -47712,16 +47712,16 @@
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.735115163585778</v>
+        <v>-2.593788845959513</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.434320929522952</v>
+        <v>2.490851456573458</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8115847362381446</v>
+        <v>0.9529110538644098</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.015674261013897</v>
+        <v>4.100470051589657</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.811445141186684</v>
+        <v>-2.670118823560419</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.401900751376365</v>
+        <v>2.458431278426871</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8115847362381446</v>
+        <v>0.9529110538644098</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.013786073907673</v>
+        <v>4.098581864483432</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.923202093801985</v>
+        <v>-2.78187577617572</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.352018199933107</v>
+        <v>2.408548726983613</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6998277836228435</v>
+        <v>0.8411541012491086</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.941552131941354</v>
+        <v>4.026347922517113</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.921361074743734</v>
+        <v>-2.780034757117468</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.351188617766559</v>
+        <v>2.407719144817065</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7010960102943119</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.940747078154387</v>
+        <v>4.025542868730146</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.053662366841287</v>
+        <v>-2.912336049215022</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.311341507793457</v>
+        <v>2.367872034843963</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7010960102943119</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.953820485020306</v>
+        <v>4.038616275596065</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763532</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.055224009656147</v>
+        <v>-2.913897692029882</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.310716850667513</v>
+        <v>2.367247377718019</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7010960102943119</v>
+        <v>0.842422327920577</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.953820485020306</v>
+        <v>4.038616275596065</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392116</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.08312479676562</v>
+        <v>-2.941798479139355</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.298080576950725</v>
+        <v>2.354611104001231</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6664990861513771</v>
+        <v>0.8078254037776422</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.931586371661547</v>
+        <v>4.016382162237306</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172527</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.205650899468514</v>
+        <v>-3.064324581842249</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.245834579846766</v>
+        <v>2.302365106897272</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5439729834484832</v>
+        <v>0.6852993010747483</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.854835154017009</v>
+        <v>3.939630944592769</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971078</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.225712220745021</v>
+        <v>-3.084385903118755</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.304516010926668</v>
+        <v>2.361046537977174</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5239116621719762</v>
+        <v>0.6652379797982413</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.909504320841609</v>
+        <v>3.994300111417368</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199806</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.482433038739845</v>
+        <v>-3.341106721113579</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.342139402730585</v>
+        <v>2.398669929781091</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.984767295357167</v>
+        <v>4.069563085932926</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622236</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.636419456515985</v>
+        <v>-3.49509313888972</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.349525104765768</v>
+        <v>2.406055631816275</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.053747564502807</v>
+        <v>4.138543355078566</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808528</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.585897552688319</v>
+        <v>-3.444571235062054</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.355785068416956</v>
+        <v>2.412315595467462</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.039798766622928</v>
+        <v>4.124594557198687</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994893</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.838372706696044</v>
+        <v>-3.697046389069778</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.26666549586928</v>
+        <v>2.323196022919786</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.051669255678342</v>
+        <v>4.136465046254101</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358298</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.107845508617752</v>
+        <v>-3.966519190991487</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.16008690961954</v>
+        <v>2.216617436670047</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4154970880281613</v>
+        <v>0.5568234056544265</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.052879790197285</v>
+        <v>4.137675580773045</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637087</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.265389580347193</v>
+        <v>-4.124063262720928</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.101191023155085</v>
+        <v>2.157721550205591</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3485952828878868</v>
+        <v>0.489921600514152</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.016860449340443</v>
+        <v>4.101656239916202</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.652163313301344</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.543353975930467</v>
+        <v>-4.402027658304202</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.985083117657966</v>
+        <v>2.041613644708471</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2589755486024026</v>
+        <v>0.4003018662286678</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.958166461505341</v>
+        <v>4.0429622520811</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215469</v>
+        <v>3.66797646721547</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.660321668569358</v>
+        <v>-4.518995350943093</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.100500097301453</v>
+        <v>2.157030624351959</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2589755486024026</v>
+        <v>0.4003018662286678</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.120370518204385</v>
+        <v>4.205166308780145</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.745039610790311</v>
+        <v>-4.603713293164046</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.061459558376886</v>
+        <v>2.117990085427392</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1738595196743562</v>
+        <v>0.3151858373006214</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.064147538811372</v>
+        <v>4.148943329387131</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.826974429059194</v>
+        <v>-4.685648111432929</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.038915048637824</v>
+        <v>2.095445575688331</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.163924774087276</v>
+        <v>0.3052510917135412</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.068416109027615</v>
+        <v>4.153211899603374</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717832</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.773236255658932</v>
+        <v>-4.788144367223278</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.069335956453831</v>
+        <v>2.063372711828093</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2176629474875381</v>
+        <v>0.2027548359231927</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.109584651523674</v>
+        <v>4.100639784585067</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616949</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.663229972181711</v>
+        <v>-4.678138083746056</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.105491357088896</v>
+        <v>2.099528112463157</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2408675194048133</v>
+        <v>0.2259594078404679</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.115660281918215</v>
+        <v>4.106715414979608</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203663</v>
+        <v>3.785578085203665</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.520170396440784</v>
+        <v>-4.53507850800513</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.16696519810724</v>
+        <v>2.161001953481502</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2488809459947926</v>
+        <v>0.2339728344304472</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.124718348594177</v>
+        <v>4.11577348165557</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436929</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.218723670968947</v>
+        <v>-4.233631782533292</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.294804771178512</v>
+        <v>2.288841526552774</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5503276714666299</v>
+        <v>0.5354195599022844</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.312847266759816</v>
+        <v>4.303902399821209</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064767</v>
+        <v>3.812650101064769</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.273678867412016</v>
+        <v>-4.288586978976362</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.273793870353994</v>
+        <v>2.267830625728256</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5503276714666299</v>
+        <v>0.5354195599022844</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.313818444512526</v>
+        <v>4.304873577573919</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859301</v>
+        <v>3.821198342859303</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.222640491405496</v>
+        <v>-4.237548602969841</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.295052125136358</v>
+        <v>2.28908888051062</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5503276714666299</v>
+        <v>0.5354195599022844</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.314661348892281</v>
+        <v>4.305716481953675</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.831748677354686</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.181501196538865</v>
+        <v>-4.196409308103211</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.330545941957156</v>
+        <v>2.324582697331417</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5914669663332607</v>
+        <v>0.5765588547689152</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.358383024686406</v>
+        <v>4.349438157747798</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82576709308562</v>
+        <v>3.825767093085622</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.070895056459263</v>
+        <v>-4.085803168023609</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.190972394112931</v>
+        <v>2.185009149487193</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7020731064128627</v>
+        <v>0.6871649948485172</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.240930704858101</v>
+        <v>4.231985837919494</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462782</v>
+        <v>3.804703121462784</v>
       </c>
       <c r="C2034" t="n">
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.201475790990106</v>
+        <v>-4.216383902554451</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.142242144374558</v>
+        <v>2.136278899748819</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5714923718820202</v>
+        <v>0.5565842603176747</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.166084308213559</v>
+        <v>4.157139441274952</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218598</v>
+        <v>3.775043021218601</v>
       </c>
       <c r="C2035" t="n">
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.036979456799144</v>
+        <v>-4.051887568363489</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.192467497127025</v>
+        <v>2.186504252501287</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5714923718820202</v>
+        <v>0.5565842603176747</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.150511127289642</v>
+        <v>4.141566260351035</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.72362336265061</v>
+        <v>3.737798729356608</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.746735483965528</v>
+        <v>3.748580561450135</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.036979456799144</v>
+        <v>-4.051887568363489</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.192467497127025</v>
+        <v>2.186504252501287</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5714923718820202</v>
+        <v>0.5565842603176747</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.739799280951896</v>
+        <v>3.741644358436503</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240725.xlsx
+++ b/tame_output/ON/bt/strategyON_20240725.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.3%</t>
+          <t>455.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-566.8%</t>
+          <t>-553.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.6%</t>
+          <t>-152.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-32.1%</t>
         </is>
       </c>
     </row>
@@ -48376,19 +48376,19 @@
         <v>3.737798729356608</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.748580561450135</v>
+        <v>3.80532683256689</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.051887568363489</v>
+        <v>-3.920234104823161</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.186504252501287</v>
+        <v>2.236876766323879</v>
       </c>
       <c r="F2036" t="n">
         <v>0.5565842603176747</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.741644358436503</v>
+        <v>4.139277388757495</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240725.xlsx
+++ b/tame_output/ON/bt/strategyON_20240725.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-70.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.6%</t>
+          <t>456.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-553.6%</t>
+          <t>-554.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.5%</t>
+          <t>-152.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.6%</t>
+          <t>-124.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-168.3%</t>
+          <t>-161.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-28.2%</t>
         </is>
       </c>
     </row>
@@ -47758,16 +47758,16 @@
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.78187577617572</v>
+        <v>-2.872372543884772</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.408548726983613</v>
+        <v>2.372350019899992</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8411541012491086</v>
+        <v>0.7506573335400564</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.026347922517113</v>
+        <v>3.972049861891682</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.780034757117468</v>
+        <v>-2.870531524826521</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.407719144817065</v>
+        <v>2.371520437733444</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7519255602115248</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.025542868730146</v>
+        <v>3.971244808104715</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.912336049215022</v>
+        <v>-3.002832816924074</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.367872034843963</v>
+        <v>2.331673327760342</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7519255602115248</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.038616275596065</v>
+        <v>3.984318214970633</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.749896851763532</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.913897692029882</v>
+        <v>-3.004394459738934</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.367247377718019</v>
+        <v>2.331048670634398</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.842422327920577</v>
+        <v>0.7519255602115248</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.038616275596065</v>
+        <v>3.984318214970633</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392116</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.941798479139355</v>
+        <v>-3.032295246848407</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.354611104001231</v>
+        <v>2.318412396917611</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8078254037776422</v>
+        <v>0.71732863606859</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.016382162237306</v>
+        <v>3.962084101611875</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172527</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.064324581842249</v>
+        <v>-3.1548213495513</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.302365106897272</v>
+        <v>2.266166399813652</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6852993010747483</v>
+        <v>0.5948025333656961</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.939630944592769</v>
+        <v>3.885332883967337</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971078</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.084385903118755</v>
+        <v>-3.174882670827807</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.361046537977174</v>
+        <v>2.324847830893553</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6652379797982413</v>
+        <v>0.574741212089189</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.994300111417368</v>
+        <v>3.940002050791937</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199806</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.341106721113579</v>
+        <v>-3.431603488822631</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.398669929781091</v>
+        <v>2.36247122269747</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4663266379453742</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.069563085932926</v>
+        <v>4.015265025307495</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622236</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.49509313888972</v>
+        <v>-3.585589906598772</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.406055631816275</v>
+        <v>2.369856924732654</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4663266379453742</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.138543355078566</v>
+        <v>4.084245294453135</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808528</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.444571235062054</v>
+        <v>-3.535068002771106</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.412315595467462</v>
+        <v>2.376116888383841</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4663266379453742</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.124594557198687</v>
+        <v>4.070296496573255</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994893</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.697046389069778</v>
+        <v>-3.78754315677883</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.323196022919786</v>
+        <v>2.286997315836166</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4663266379453742</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.136465046254101</v>
+        <v>4.082166985628669</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358298</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.966519190991487</v>
+        <v>-4.057015958700538</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.216617436670047</v>
+        <v>2.180418729586426</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5568234056544265</v>
+        <v>0.4663266379453742</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.137675580773045</v>
+        <v>4.083377520147613</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637087</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.124063262720928</v>
+        <v>-4.21456003042998</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.157721550205591</v>
+        <v>2.121522843121971</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.489921600514152</v>
+        <v>0.3994248328050997</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.101656239916202</v>
+        <v>4.04735817929077</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301344</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.402027658304202</v>
+        <v>-4.492524426013254</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.041613644708471</v>
+        <v>2.005414937624851</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.3098050985196155</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.0429622520811</v>
+        <v>3.988664191455669</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66797646721547</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.518995350943093</v>
+        <v>-4.609492118652144</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.157030624351959</v>
+        <v>2.120831917268339</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4003018662286678</v>
+        <v>0.3098050985196155</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.205166308780145</v>
+        <v>4.150868248154713</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456692</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.603713293164046</v>
+        <v>-4.694210060873098</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.117990085427392</v>
+        <v>2.081791378343771</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3151858373006214</v>
+        <v>0.2246890695915691</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.148943329387131</v>
+        <v>4.094645268761699</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253288</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.685648111432929</v>
+        <v>-4.776144879141981</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.095445575688331</v>
+        <v>2.05924686860471</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3052510917135412</v>
+        <v>0.2147543240044889</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.153211899603374</v>
+        <v>4.098913838977943</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717832</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.788144367223278</v>
+        <v>-4.722406705741719</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.063372711828093</v>
+        <v>2.089667776420717</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2027548359231927</v>
+        <v>0.268492497404751</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.100639784585067</v>
+        <v>4.140082381474002</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616949</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.678138083746056</v>
+        <v>-4.612400422264497</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.099528112463157</v>
+        <v>2.125823177055781</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2259594078404679</v>
+        <v>0.2916970693220262</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.106715414979608</v>
+        <v>4.146158011868543</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203665</v>
+        <v>3.785578085203664</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.53507850800513</v>
+        <v>-4.469340846523572</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.161001953481502</v>
+        <v>2.187297018074125</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2339728344304472</v>
+        <v>0.2997104959120055</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.11577348165557</v>
+        <v>4.155216078544504</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.233631782533292</v>
+        <v>-4.167894121051734</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.288841526552774</v>
+        <v>2.315136591145396</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5354195599022844</v>
+        <v>0.6011572213838428</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.303902399821209</v>
+        <v>4.343344996710144</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064769</v>
+        <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.288586978976362</v>
+        <v>-4.222849317494804</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.267830625728256</v>
+        <v>2.294125690320879</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5354195599022844</v>
+        <v>0.6011572213838428</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.304873577573919</v>
+        <v>4.344316174462854</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859303</v>
+        <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.237548602969841</v>
+        <v>-4.171810941488284</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.28908888051062</v>
+        <v>2.315383945103243</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5354195599022844</v>
+        <v>0.6011572213838428</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.305716481953675</v>
+        <v>4.34515907884261</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354686</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.196409308103211</v>
+        <v>-4.130671646621653</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.324582697331417</v>
+        <v>2.350877761924041</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5765588547689152</v>
+        <v>0.6422965162504736</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.349438157747798</v>
+        <v>4.388880754636733</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085622</v>
+        <v>3.82576709308562</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.085803168023609</v>
+        <v>-4.020065506542051</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.185009149487193</v>
+        <v>2.211304214079816</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6871649948485172</v>
+        <v>0.7529026563300756</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.231985837919494</v>
+        <v>4.271428434808429</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462784</v>
+        <v>3.804703121462782</v>
       </c>
       <c r="C2034" t="n">
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.216383902554451</v>
+        <v>-4.150646241072893</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.136278899748819</v>
+        <v>2.162573964341442</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5565842603176747</v>
+        <v>0.6223219217992331</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.157139441274952</v>
+        <v>4.196582038163887</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218601</v>
+        <v>3.775043021218599</v>
       </c>
       <c r="C2035" t="n">
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.051887568363489</v>
+        <v>-3.986149906881931</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.186504252501287</v>
+        <v>2.21279931709391</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5565842603176747</v>
+        <v>0.6223219217992331</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.141566260351035</v>
+        <v>4.18100885723997</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.737798729356608</v>
+        <v>3.784879887875134</v>
       </c>
       <c r="C2036" t="n">
         <v>3.80532683256689</v>
       </c>
       <c r="D2036" t="n">
-        <v>-3.920234104823161</v>
+        <v>-3.930210256876202</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.236876766323879</v>
+        <v>2.232886305502662</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5565842603176747</v>
+        <v>0.6223219217992331</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.139277388757495</v>
+        <v>4.17871998564643</v>
       </c>
     </row>
   </sheetData>
